--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\项目文件夹\python项目\TestAutomationframework\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC971A1-CA4D-4A07-BFEF-4523C4AF27F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83704224-5E0B-4B22-81F3-65814D6D1179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>编号</t>
   </si>
@@ -315,6 +315,10 @@
       </rPr>
       <t>}</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$.code</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -689,6 +693,8 @@
     <col min="6" max="6" width="31.875" customWidth="1"/>
     <col min="7" max="7" width="11.75" customWidth="1"/>
     <col min="10" max="10" width="56.375" customWidth="1"/>
+    <col min="11" max="11" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="12.125" customWidth="1"/>
     <col min="14" max="14" width="20.875" customWidth="1"/>
     <col min="15" max="15" width="21.25" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
@@ -833,7 +839,9 @@
         <v>37</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="M3" s="3">
         <v>1</v>
       </c>
@@ -871,7 +879,9 @@
         <v>43</v>
       </c>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="M4" s="3">
         <v>0</v>
       </c>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83704224-5E0B-4B22-81F3-65814D6D1179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8030F84F-71E4-4555-96CB-F73A93D283D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5235" yWindow="2655" windowWidth="21600" windowHeight="11940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,300 +25,317 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+  <si>
+    <t>模块</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>标题</t>
+  </si>
+  <si>
+    <t>请求方式</t>
+  </si>
+  <si>
+    <t>路径</t>
+  </si>
+  <si>
+    <t>请求头</t>
+  </si>
+  <si>
+    <t>url参数</t>
+  </si>
+  <si>
+    <t>data参数</t>
+  </si>
+  <si>
+    <t>json参数</t>
+  </si>
+  <si>
+    <t>文件参数</t>
+  </si>
+  <si>
+    <t>校验字段</t>
+  </si>
+  <si>
+    <t>预期结果</t>
+  </si>
+  <si>
+    <t>数据库校验内容</t>
+  </si>
+  <si>
+    <t>数据库预期结果</t>
+  </si>
+  <si>
+    <t>json提取</t>
+  </si>
+  <si>
+    <t>sql提取</t>
+  </si>
+  <si>
+    <t>是否执行</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>params</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>files</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>sql_check</t>
+  </si>
+  <si>
+    <t>sql_expected</t>
+  </si>
+  <si>
+    <t>jsonExData</t>
+  </si>
+  <si>
+    <t>sqlExData</t>
+  </si>
+  <si>
+    <t>登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误的密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'username'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'admin'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'password'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'123456'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t>is_true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>headers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/employee/login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'username'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'admin'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'password'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'654321'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14.3"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$.code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"TOKEN":"$..token"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>编号</t>
-  </si>
-  <si>
-    <t>模块</t>
-  </si>
-  <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>标题</t>
-  </si>
-  <si>
-    <t>请求方式</t>
-  </si>
-  <si>
-    <t>路径</t>
-  </si>
-  <si>
-    <t>请求头</t>
-  </si>
-  <si>
-    <t>url参数</t>
-  </si>
-  <si>
-    <t>data参数</t>
-  </si>
-  <si>
-    <t>json参数</t>
-  </si>
-  <si>
-    <t>文件参数</t>
-  </si>
-  <si>
-    <t>校验字段</t>
-  </si>
-  <si>
-    <t>预期结果</t>
-  </si>
-  <si>
-    <t>数据库校验内容</t>
-  </si>
-  <si>
-    <t>数据库预期结果</t>
-  </si>
-  <si>
-    <t>json提取</t>
-  </si>
-  <si>
-    <t>sql提取</t>
-  </si>
-  <si>
-    <t>是否执行</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>feature</t>
-  </si>
-  <si>
-    <t>story</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>params</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>files</t>
-  </si>
-  <si>
-    <t>check</t>
-  </si>
-  <si>
-    <t>sql_check</t>
-  </si>
-  <si>
-    <t>sql_expected</t>
-  </si>
-  <si>
-    <t>jsonExData</t>
-  </si>
-  <si>
-    <t>sqlExData</t>
-  </si>
-  <si>
-    <t>登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登录成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登录失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>错误的密码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>post</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'username'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'admin'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'password'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'123456'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>}</t>
-    </r>
-  </si>
-  <si>
-    <t>is_true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>path</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>expected</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>headers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/admin/employee/login</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'username'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'admin'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'password'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FF6AAB73"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>'654321'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14.3"/>
-        <color rgb="FFBCBEC4"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>$.code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select name from employee WHERE username = 'admin'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id":"select id from employee where username = 'admin'"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -695,122 +712,122 @@
     <col min="10" max="10" width="56.375" customWidth="1"/>
     <col min="11" max="11" width="15.25" customWidth="1"/>
     <col min="13" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="58.5" customWidth="1"/>
     <col min="15" max="15" width="21.25" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="19.125" customWidth="1"/>
+    <col min="17" max="17" width="56.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="18.75">
@@ -818,37 +835,45 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M3" s="3">
         <v>1</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="N3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="R3" s="3" t="b">
         <v>1</v>
       </c>
@@ -858,29 +883,29 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M4" s="3">
         <v>0</v>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8030F84F-71E4-4555-96CB-F73A93D283D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D5DEA-2073-4404-8A05-5414467BC0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="2655" windowWidth="21600" windowHeight="11940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
   <si>
     <t>模块</t>
   </si>
@@ -137,6 +137,26 @@
   </si>
   <si>
     <t>post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>headers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/employee/login</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -204,7 +224,7 @@
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
       </rPr>
-      <t>'123456'</t>
+      <t>'654321'</t>
     </r>
     <r>
       <rPr>
@@ -215,25 +235,98 @@
       </rPr>
       <t>}</t>
     </r>
-  </si>
-  <si>
-    <t>is_true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>path</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>expected</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>headers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/admin/employee/login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$.code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"TOKEN":"$..token"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select name from employee WHERE username = 'admin'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id":"select id from employee where username = 'admin'"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/plant/plantQueryById</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"id":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿植</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无权限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$.msg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无TOKEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据id获取信息失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据id获取信息成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$..name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小叶栀子花盆栽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{'token':'{{TOKEN}}'}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路径参数根据id获取信息成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路径参数获取成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"PLANT_ID":"$..id"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/plant/plantQueryById/{{PLANT_ID}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -301,7 +394,7 @@
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
       </rPr>
-      <t>'654321'</t>
+      <t>'123456'</t>
     </r>
     <r>
       <rPr>
@@ -315,27 +408,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>$.code</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"TOKEN":"$..token"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>select name from employee WHERE username = 'admin'</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>管理员</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"id":"select id from employee where username = 'admin'"}</t>
+    <t>/admin/common/localUpload</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件上传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件上传成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ 'file':('1.png',open('./file/img.png','rb'),'png') }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -415,12 +500,12 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,16 +787,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="23.125" customWidth="1"/>
-    <col min="6" max="6" width="31.875" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="10" max="10" width="56.375" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="23.875" customWidth="1"/>
+    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
+    <col min="10" max="10" width="63.125" customWidth="1"/>
+    <col min="11" max="11" width="68.375" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
     <col min="14" max="14" width="58.5" customWidth="1"/>
     <col min="15" max="15" width="21.25" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
@@ -720,7 +805,7 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -791,10 +876,10 @@
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>22</v>
@@ -812,7 +897,7 @@
         <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>27</v>
@@ -827,96 +912,622 @@
         <v>30</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="18.75">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="18.75">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R3" s="3" t="b">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18.75">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="3" t="s">
+    <row r="6" spans="1:18">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="4" t="s">
+      <c r="F8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3" t="b">
+      <c r="M8" s="2">
         <v>1</v>
       </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D5DEA-2073-4404-8A05-5414467BC0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCC43F5-5833-4811-8241-9E769A3F03C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5235" yWindow="2655" windowWidth="21600" windowHeight="11940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCC43F5-5833-4811-8241-9E769A3F03C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0F6CC6-4281-4A20-8A8B-9DAB44C63183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="2655" windowWidth="21600" windowHeight="11940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
   <si>
     <t>模块</t>
   </si>
@@ -421,6 +421,262 @@
   </si>
   <si>
     <t>{ 'file':('1.png',open('./file/img.png','rb'),'png') }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登陆成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿植接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据分页查询条件查询植物列表</t>
+  </si>
+  <si>
+    <t>获取所有植物列表</t>
+  </si>
+  <si>
+    <t>查询植物分类</t>
+  </si>
+  <si>
+    <t>更新植物状态</t>
+  </si>
+  <si>
+    <t>根据ID查询植物详情</t>
+  </si>
+  <si>
+    <t>更新植物信息</t>
+  </si>
+  <si>
+    <t>根据ID删除植物</t>
+  </si>
+  <si>
+    <t>批量删除植物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加新植物</t>
+  </si>
+  <si>
+    <t>获取植物图片</t>
+  </si>
+  <si>
+    <t>/admin/plant/plantQueryPage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{'username':'admin','password':'123456'}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/plant/GetPlantAllList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/plant/plantCategory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/plant/plantStatus</t>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"id"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"2"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"status"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"id"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"2"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"status"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "name": "",
+    "category": "",
+    "mixPrice": 1,
+    "maxPrice": 1,
+    "page": 1,
+    "pageSize": 10
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/auth/captcha</t>
+  </si>
+  <si>
+    <t>{"SN":"$..sn","IMAGE":"$..image"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功获取验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/auth/login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{'Content-Type': 'application/x-www-form-urlencoded;charset=UTF-8'}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{'password':'admin','username':'1000@admin','sn':'{{SN}}','captcha':dddd_ocr_text('{{IMAGE}}')}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,7 +684,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +709,49 @@
       <sz val="14.3"/>
       <color rgb="FF6AAB73"/>
       <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0451A5"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF098658"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -497,14 +796,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,747 +1111,1527 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="23.875" customWidth="1"/>
-    <col min="6" max="6" width="35.875" customWidth="1"/>
-    <col min="7" max="7" width="26.75" customWidth="1"/>
-    <col min="10" max="10" width="63.125" customWidth="1"/>
-    <col min="11" max="11" width="68.375" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="14" width="58.5" customWidth="1"/>
-    <col min="15" max="15" width="21.25" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="56.5" customWidth="1"/>
+    <col min="1" max="1" width="6.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9" style="2"/>
+    <col min="13" max="13" width="9" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15" style="2" customWidth="1"/>
+    <col min="17" max="17" width="14.875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.125" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" ht="28.5">
+      <c r="A1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18.75">
-      <c r="A3" s="2">
+    <row r="3" spans="1:18" ht="57" hidden="1">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
       <c r="J3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>1</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="R3" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="18.75">
-      <c r="A4" s="2">
+      <c r="R3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="56.25" hidden="1">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
       <c r="J4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="K4" s="1"/>
+      <c r="L4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="1">
         <v>0</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="b">
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="28.5" hidden="1">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="28.5" hidden="1">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="42.75" hidden="1">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="71.25" hidden="1">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="28.5" hidden="1">
+      <c r="A9" s="1">
+        <v>100</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="140.25" hidden="1" customHeight="1">
+      <c r="A10" s="1">
+        <v>101</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="33" hidden="1" customHeight="1">
+      <c r="A11" s="1">
+        <v>102</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="b">
+      <c r="F11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="28.5" hidden="1">
+      <c r="A12" s="1">
+        <v>103</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="b">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="28.5" hidden="1">
+      <c r="A13" s="1">
+        <v>104</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="28.5" hidden="1">
+      <c r="A14" s="1">
+        <v>105</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="42.75" hidden="1">
+      <c r="A15" s="1">
+        <v>106</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="28.5" hidden="1">
+      <c r="A16" s="1">
+        <v>107</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="28.5" hidden="1">
+      <c r="A17" s="1">
+        <v>108</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="28.5" hidden="1">
+      <c r="A18" s="1">
+        <v>109</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="28.5" hidden="1">
+      <c r="A19" s="1">
+        <v>110</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="28.5" hidden="1">
+      <c r="A20" s="1">
+        <v>111</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="42.75" hidden="1">
+      <c r="A21" s="1">
+        <v>112</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="28.5">
+      <c r="A22" s="1">
+        <v>113</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="b">
+      <c r="F22" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" s="1">
+        <v>200</v>
+      </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="2" t="s">
+    <row r="23" spans="1:18" ht="71.25">
+      <c r="A23" s="1">
+        <v>114</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="F23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M23" s="1">
+        <v>200</v>
+      </c>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
+      <c r="A24" s="1">
+        <v>115</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
+      <c r="A25" s="1">
+        <v>116</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
+      <c r="A26" s="1">
+        <v>117</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="1">
+        <v>118</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="1">
+        <v>119</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="1">
+        <v>120</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="1">
+        <v>121</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="1">
+        <v>122</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="1">
+        <v>123</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="1">
+        <v>124</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="1">
+        <v>125</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="1">
+        <v>126</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="1">
+        <v>127</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="1">
+        <v>128</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="1">
+        <v>129</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="1">
+        <v>130</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="1">
+        <v>131</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="1">
+        <v>132</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="1">
+        <v>133</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="1">
+        <v>134</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="1">
+        <v>135</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="1">
+        <v>136</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="1">
+        <v>137</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="1">
+        <v>138</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="1">
+        <v>139</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="1">
+        <v>140</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="1">
+        <v>141</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0F6CC6-4281-4A20-8A8B-9DAB44C63183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84E2CF5-B4FE-479E-826C-C218EC34F7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1247,7 +1247,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="57" hidden="1">
+    <row r="3" spans="1:18" ht="57">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1292,10 +1292,10 @@
         <v>47</v>
       </c>
       <c r="R3" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="56.25" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="56.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="28.5" hidden="1">
+    <row r="5" spans="1:18" ht="28.5">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="28.5" hidden="1">
+    <row r="6" spans="1:18" ht="28.5">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="42.75" hidden="1">
+    <row r="7" spans="1:18" ht="42.75">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="71.25" hidden="1">
+    <row r="8" spans="1:18" ht="71.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="28.5" hidden="1">
+    <row r="9" spans="1:18" ht="28.5">
       <c r="A9" s="1">
         <v>100</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="140.25" hidden="1" customHeight="1">
+    <row r="10" spans="1:18" ht="140.25" customHeight="1">
       <c r="A10" s="1">
         <v>101</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="33" hidden="1" customHeight="1">
+    <row r="11" spans="1:18" ht="33" customHeight="1">
       <c r="A11" s="1">
         <v>102</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="28.5" hidden="1">
+    <row r="12" spans="1:18" ht="28.5">
       <c r="A12" s="1">
         <v>103</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="28.5" hidden="1">
+    <row r="13" spans="1:18" ht="28.5">
       <c r="A13" s="1">
         <v>104</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="28.5" hidden="1">
+    <row r="14" spans="1:18" ht="28.5">
       <c r="A14" s="1">
         <v>105</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="42.75" hidden="1">
+    <row r="15" spans="1:18" ht="42.75">
       <c r="A15" s="1">
         <v>106</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="28.5" hidden="1">
+    <row r="16" spans="1:18" ht="28.5">
       <c r="A16" s="1">
         <v>107</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="28.5" hidden="1">
+    <row r="17" spans="1:18" ht="28.5">
       <c r="A17" s="1">
         <v>108</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="28.5" hidden="1">
+    <row r="18" spans="1:18" ht="28.5">
       <c r="A18" s="1">
         <v>109</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="28.5" hidden="1">
+    <row r="19" spans="1:18" ht="28.5">
       <c r="A19" s="1">
         <v>110</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="28.5" hidden="1">
+    <row r="20" spans="1:18" ht="28.5">
       <c r="A20" s="1">
         <v>111</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="42.75" hidden="1">
+    <row r="21" spans="1:18" ht="42.75">
       <c r="A21" s="1">
         <v>112</v>
       </c>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="71.25">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84E2CF5-B4FE-479E-826C-C218EC34F7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C53286-A2FD-4B73-9C36-8F7931240EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TestAutomationframework\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\TestAutomationframework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C53286-A2FD-4B73-9C36-8F7931240EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A0EF5E-5DDA-408A-AED5-D6C9CF42E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3615" yWindow="2145" windowWidth="21600" windowHeight="11940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="100">
   <si>
     <t>模块</t>
   </si>
@@ -677,6 +677,14 @@
   </si>
   <si>
     <t>{'password':'admin','username':'1000@admin','sn':'{{SN}}','captcha':dddd_ocr_text('{{IMAGE}}')}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>['$.code']</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1274,10 +1282,10 @@
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="1">
-        <v>1</v>
+        <v>98</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>45</v>
@@ -1292,7 +1300,7 @@
         <v>47</v>
       </c>
       <c r="R3" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="56.25">
